--- a/documents/Alexandre_Le_Guern_tab_E5.xlsx
+++ b/documents/Alexandre_Le_Guern_tab_E5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff2\Documents\GitHub\Portfolio-Slam\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6F005B-8077-4F39-8EBC-D0AAFED45230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1076E538-3D3F-4B6E-A6D8-4F272B0118AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="47">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>N° candidat : 02248905640</t>
+  </si>
+  <si>
+    <t>FLD animation</t>
   </si>
 </sst>
 </file>
@@ -682,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -712,12 +715,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -783,68 +780,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -858,11 +798,80 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1128,7 +1137,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z999"/>
+  <dimension ref="A1:Z997"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.33203125" customWidth="1"/>
@@ -1140,44 +1149,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="12"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="42" t="s">
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="44"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1186,10 +1195,10 @@
       <c r="A4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1201,50 +1210,50 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="52" t="s">
+      <c r="D5" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="F5" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="52" t="s">
+      <c r="G5" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="53" t="s">
+      <c r="H5" s="33" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="41"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="55" t="s">
+      <c r="A6" s="55"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="34" t="s">
         <v>21</v>
       </c>
       <c r="K6" s="1"/>
@@ -1265,16 +1274,16 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="58" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="60"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1295,24 +1304,24 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="58" t="s">
+      <c r="D8" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58" t="s">
+      <c r="E8" s="37"/>
+      <c r="F8" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58" t="s">
+      <c r="G8" s="37"/>
+      <c r="H8" s="37" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="1"/>
@@ -1338,7 +1347,7 @@
       <c r="A9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1375,10 +1384,10 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>35</v>
+      <c r="A10" s="38" t="s">
+        <v>46</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="39" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="6" t="s">
@@ -1391,10 +1400,10 @@
       <c r="F10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="6"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1415,16 +1424,26 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37" t="s">
-        <v>28</v>
+      <c r="A11" s="9" t="s">
+        <v>35</v>
       </c>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="39"/>
+      <c r="B11" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="6"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1445,18 +1464,16 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
-        <v>29</v>
+      <c r="A12" s="60" t="s">
+        <v>28</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="32"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="62"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1477,22 +1494,18 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>36</v>
+      <c r="A13" s="22" t="s">
+        <v>29</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="33" t="s">
-        <v>25</v>
+      <c r="B13" s="13" t="s">
+        <v>30</v>
       </c>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33" t="s">
-        <v>25</v>
-      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="30"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1514,21 +1527,21 @@
     </row>
     <row r="14" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="E14" s="31"/>
+      <c r="F14" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="23" t="s">
+      <c r="G14" s="31"/>
+      <c r="H14" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="23"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1549,20 +1562,22 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
-        <v>38</v>
+      <c r="A15" s="9" t="s">
+        <v>37</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23" t="s">
+      <c r="F15" s="21" t="s">
         <v>25</v>
       </c>
+      <c r="G15" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="21"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1583,20 +1598,20 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>39</v>
+      <c r="A16" s="20" t="s">
+        <v>38</v>
       </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23" t="s">
+      <c r="B16" s="14"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23" t="s">
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="23"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1616,15 +1631,21 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="20"/>
+    <row r="17" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="21"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1645,16 +1666,14 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="36"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1675,18 +1694,16 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
-        <v>32</v>
+      <c r="A19" s="48" t="s">
+        <v>31</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="32"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="50"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1707,22 +1724,18 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
-        <v>40</v>
+      <c r="A20" s="22" t="s">
+        <v>32</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="27" t="s">
-        <v>25</v>
+      <c r="B20" s="7" t="s">
+        <v>33</v>
       </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="28" t="s">
-        <v>25</v>
-      </c>
+      <c r="C20" s="24"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="30"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1743,20 +1756,22 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
-        <v>41</v>
+      <c r="A21" s="23" t="s">
+        <v>40</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23" t="s">
+      <c r="B21" s="8"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="E21" s="25"/>
+      <c r="F21" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="23"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26" t="s">
+        <v>25</v>
+      </c>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1777,20 +1792,20 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>42</v>
+      <c r="A22" s="20" t="s">
+        <v>41</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="23" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H22" s="23"/>
+      <c r="H22" s="21"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1811,20 +1826,20 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
-        <v>43</v>
+      <c r="A23" s="9" t="s">
+        <v>42</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23" t="s">
+      <c r="B23" s="14"/>
+      <c r="C23" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23" t="s">
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H23" s="23"/>
+      <c r="H23" s="21"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1845,20 +1860,20 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="22" t="s">
-        <v>44</v>
+      <c r="A24" s="20" t="s">
+        <v>43</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="23" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23" t="s">
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="23"/>
+      <c r="H24" s="21"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1879,14 +1894,20 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+      <c r="A25" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="21"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -1906,7 +1927,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2102,7 +2123,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2130,7 +2151,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2139,24 +2160,6 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
     </row>
     <row r="35" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
@@ -2167,24 +2170,6 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
     </row>
     <row r="36" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
@@ -11689,21 +11674,19 @@
     <row r="995" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="996" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="997" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="998" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A11:H11"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>

--- a/documents/Alexandre_Le_Guern_tab_E5.xlsx
+++ b/documents/Alexandre_Le_Guern_tab_E5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeff2\Documents\GitHub\Portfolio-Slam\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1076E538-3D3F-4B6E-A6D8-4F272B0118AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B86F38-7A36-4268-B620-ACA6EF3B6BEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="48">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>FLD animation</t>
+  </si>
+  <si>
+    <t>09/03/2026 01/05/2026</t>
   </si>
 </sst>
 </file>
@@ -804,30 +807,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -872,6 +851,30 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1149,56 +1152,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="40"/>
+      <c r="H1" s="55"/>
     </row>
     <row r="2" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
     </row>
     <row r="3" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="45" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="46"/>
-      <c r="H3" s="47"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="62"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="53"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1210,10 +1213,10 @@
       </c>
     </row>
     <row r="5" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+      <c r="A5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="48" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="32" t="s">
@@ -1236,8 +1239,8 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="324.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
-      <c r="B6" s="57"/>
+      <c r="A6" s="47"/>
+      <c r="B6" s="49"/>
       <c r="C6" s="34" t="s">
         <v>16</v>
       </c>
@@ -1274,16 +1277,16 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="58" t="s">
+      <c r="A7" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1428,7 +1431,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>25</v>
@@ -1464,16 +1467,16 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="60" t="s">
+      <c r="A12" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="61"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="62"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="53"/>
+      <c r="D12" s="53"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="54"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1694,16 +1697,16 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="50"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="42"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -11676,17 +11679,17 @@
     <row r="997" ht="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0.511811023622047" footer="0.511811023622047"/>
